--- a/dati/CONSEGNE/CONSEGNE_16-04-2026/punti_consegna.xlsx
+++ b/dati/CONSEGNE/CONSEGNE_16-04-2026/punti_consegna.xlsx
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>45.3887674</v>
+        <v>45.38758191504752</v>
       </c>
       <c r="J20" t="n">
-        <v>11.6501101</v>
+        <v>11.65114722038251</v>
       </c>
     </row>
     <row r="21">
